--- a/aq_files/0419.xlsx
+++ b/aq_files/0419.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbench Scenario MCQs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,9 +49,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -135,44 +134,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -199,14 +198,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -233,6 +250,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -244,166 +279,142 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
@@ -413,48 +424,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Q.No</t>
+          <t>Question No.</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Topic</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Scenario Question</t>
+          <t>Question Type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Option A</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Option B</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Option C</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Option D</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Answer</t>
         </is>
       </c>
     </row>
@@ -464,37 +485,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>You are configuring a new MySQL connection in MySQL Workbench. The server is running on default settings. Which port number should you enter to successfully connect?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8080</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5432</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3306</t>
+          <t>DATASET</t>
         </is>
       </c>
     </row>
@@ -504,37 +505,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>While writing a query in MySQL Workbench, you want to execute only a selected portion of the SQL code instead of the entire script. Which option or shortcut should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Execute Selection (Ctrl+Enter)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Run All</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Compile</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Debug</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Execute Selection (Ctrl+Enter)</t>
+          <t>DATA</t>
         </is>
       </c>
     </row>
@@ -544,37 +525,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>After executing a SELECT query in MySQL Workbench, you are unable to see the output. Where should you look to view the query results?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Result Grid</t>
+          <t>Create a basic workflow to demonstrate Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Logs</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Editor</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Result Grid</t>
+          <t>Workflow Setup</t>
         </is>
       </c>
     </row>
@@ -584,37 +555,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A user is unable to connect to the MySQL server from Workbench. What is the first thing they should verify before troubleshooting further?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Check if MySQL server is running</t>
+          <t>Perform a step-by-step practical exercise using Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rewrite the query</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Restart system</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Change UI theme</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Check if MySQL server is running</t>
+          <t>Hands-On Execution</t>
         </is>
       </c>
     </row>
@@ -624,37 +585,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>You need to import a dataset from a dump file into MySQL Workbench for analysis. Which feature should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data Import</t>
+          <t>Build a small example that applies Data Preparation for Variance Analysis to sample data.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SQL Editor</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Server Logs</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Data Import</t>
+          <t>Example Building</t>
         </is>
       </c>
     </row>
@@ -664,37 +615,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>You want to create a backup of an existing database in MySQL Workbench. Which feature should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Data Export</t>
+          <t>Demonstrate how to validate the output produced by Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Save Query</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Transfer Wizard</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Logs Panel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Data Export</t>
+          <t>Output Validation</t>
         </is>
       </c>
     </row>
@@ -704,37 +645,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>While exploring a database schema, you want to view all tables and their structure. Which panel in MySQL Workbench should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Configure the minimum setup required to start Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Output Panel</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logs Panel</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Navigator Panel</t>
+          <t>Configuration</t>
         </is>
       </c>
     </row>
@@ -744,37 +675,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>You need to modify the structure of an existing table by adding a new column. Which SQL operation should you perform in MySQL Workbench?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ALTER TABLE</t>
+          <t>Show how to prepare the input data or resources for Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>INSERT</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ALTER TABLE</t>
+          <t>Input Preparation</t>
         </is>
       </c>
     </row>
@@ -784,37 +705,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>You want to review previously executed queries in MySQL Workbench for debugging purposes. Where can you find this information?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Query History Panel</t>
+          <t>Execute Data Preparation for Variance Analysis and document each major step clearly.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Output Panel</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Query History Panel</t>
+          <t>Procedure Documentation</t>
         </is>
       </c>
     </row>
@@ -824,37 +735,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>While working on multiple queries, you want a quick way to execute the current query without using the mouse. Which shortcut should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ctrl+Enter</t>
+          <t>Apply Data Preparation for Variance Analysis to solve a simple business problem.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ctrl+S</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Ctrl+X</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Ctrl+Enter</t>
+          <t>Business Application</t>
         </is>
       </c>
     </row>
@@ -864,37 +765,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You are connected to a MySQL database, but your queries are failing due to permission issues. What is the most appropriate step to resolve this?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Check user privileges and permissions</t>
+          <t>Create a reusable template for repeating Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Restart Workbench</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Change UI theme</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Reinstall MySQL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Check user privileges and permissions</t>
+          <t>Template Creation</t>
         </is>
       </c>
     </row>
@@ -904,37 +795,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You created a new schema but it is not visible in the list of schemas. What should you do to resolve this issue?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Refresh the Navigator panel</t>
+          <t>Demonstrate how to troubleshoot a failed Data Preparation for Variance Analysis workflow.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Restart system</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rewrite query</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Reconnect internet</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Refresh the Navigator panel</t>
+          <t>Troubleshooting</t>
         </is>
       </c>
     </row>
@@ -944,37 +825,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>After executing a query, no results are displayed even though the query syntax is correct. What is the most likely reason?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Query conditions do not match any data</t>
+          <t>Perform Data Preparation for Variance Analysis and explain the expected result at each stage.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Workbench error</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>System crash</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Port issue</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Query conditions do not match any data</t>
+          <t>Expected Outcomes</t>
         </is>
       </c>
     </row>
@@ -984,37 +855,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You want to modify only a specific column's datatype in an existing table. Which approach should you take?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Use ALTER TABLE with MODIFY</t>
+          <t>Create a checklist to verify that Data Preparation for Variance Analysis was performed correctly.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drop and recreate table</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Insert new values</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Select query</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Use ALTER TABLE with MODIFY</t>
+          <t>Quality Checks</t>
         </is>
       </c>
     </row>
@@ -1024,37 +885,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>While connecting to a remote MySQL server, which credentials are mandatory for successful authentication?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Username and Password</t>
+          <t>Use Data Preparation for Variance Analysis to compare two different scenarios or inputs.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Only username</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Only password</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Username and Password</t>
+          <t>Scenario Comparison</t>
         </is>
       </c>
     </row>
@@ -1064,37 +915,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You notice that your query execution is slower than expected. Which tool in MySQL Workbench can help analyze query performance?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Performance/Query Analyzer</t>
+          <t>Demonstrate how to optimize the workflow used in Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Logs Panel</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Performance/Query Analyzer</t>
+          <t>Optimization</t>
         </is>
       </c>
     </row>
@@ -1104,37 +945,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>If the MySQL service is stopped, what will happen when you try to connect using Workbench?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Connection will fail</t>
+          <t>Perform Data Preparation for Variance Analysis using a constrained or minimal dataset.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Query executes</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Workbench crashes</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Nothing happens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Connection will fail</t>
+          <t>Lightweight Execution</t>
         </is>
       </c>
     </row>
@@ -1144,37 +975,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>You want to delete an entire table including its structure from the database. Which SQL command should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DROP TABLE</t>
+          <t>Create a summary view or report after completing Data Preparation for Variance Analysis.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUNCATE</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>REMOVE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>DROP TABLE</t>
+          <t>Result Reporting</t>
         </is>
       </c>
     </row>
@@ -1184,37 +1005,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>You are connected to the database but unable to execute queries on a specific schema. What is the most appropriate troubleshooting step?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Verify schema selection and permissions</t>
+          <t>Demonstrate how to reuse outputs from Data Preparation for Variance Analysis in the next task.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Restart system</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Change port</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Ignore issue</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Verify schema selection and permissions</t>
+          <t>Workflow Linking</t>
         </is>
       </c>
     </row>
@@ -1224,37 +1035,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>While working in MySQL Workbench, you want to execute multiple queries sequentially from a script. Which option should you use?</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Execute All/Run Script</t>
+          <t>Apply Data Preparation for Variance Analysis in a timed exercise and record the outcome.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Execute Selection</t>
+          <t>Course CDA | DAA-131/VARIANCE AND FREQUENCY ANALYSIS/Data Preparation for Variance Analysis</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Compile</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Debug</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Execute All/Run Script</t>
+          <t>Timed Practice</t>
         </is>
       </c>
     </row>
